--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N58_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N58_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.70683785111977</v>
+        <v>5.802361150806963</v>
       </c>
       <c r="D2" t="n">
-        <v>15.98980188033408</v>
+        <v>2.598342805554288</v>
       </c>
       <c r="E2" t="n">
-        <v>16.72670196378699</v>
+        <v>2.718089069115386</v>
       </c>
       <c r="F2" t="n">
-        <v>5.401359002500466</v>
+        <v>0.8777208379063257</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>9.160238635963935</v>
+        <v>1.48853877834414</v>
       </c>
       <c r="D3" t="n">
-        <v>5.657126155543516</v>
+        <v>0.9192830002758213</v>
       </c>
       <c r="E3" t="n">
-        <v>16.72670196378699</v>
+        <v>2.718089069115386</v>
       </c>
       <c r="F3" t="n">
-        <v>5.401359002500466</v>
+        <v>0.8777208379063257</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.48967448013886</v>
+        <v>3.654572103022566</v>
       </c>
       <c r="D4" t="n">
-        <v>20.54332649150124</v>
+        <v>3.338290554868951</v>
       </c>
       <c r="E4" t="n">
-        <v>16.72670196378699</v>
+        <v>2.718089069115386</v>
       </c>
       <c r="F4" t="n">
-        <v>5.401359002500466</v>
+        <v>0.8777208379063257</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>54.42655601817921</v>
+        <v>8.844315352954123</v>
       </c>
       <c r="D5" t="n">
-        <v>14.72955610821128</v>
+        <v>2.393552867584333</v>
       </c>
       <c r="E5" t="n">
-        <v>16.72670196378699</v>
+        <v>2.718089069115386</v>
       </c>
       <c r="F5" t="n">
-        <v>5.401359002500466</v>
+        <v>0.8777208379063257</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
